--- a/data/raw/cpi.xlsx
+++ b/data/raw/cpi.xlsx
@@ -17,89 +17,89 @@
     <sheet name="Enquiries" sheetId="2" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="A130392355X">Data1!$H$1:$H$10,Data1!$H$11:$H$32</definedName>
-    <definedName name="A130392355X_Data">Data1!$H$11:$H$32</definedName>
-    <definedName name="A130392355X_Latest">Data1!$H$32</definedName>
-    <definedName name="A130392356A">Data1!$Q$1:$Q$10,Data1!$Q$23:$Q$32</definedName>
-    <definedName name="A130392356A_Data">Data1!$Q$23:$Q$32</definedName>
-    <definedName name="A130392356A_Latest">Data1!$Q$32</definedName>
-    <definedName name="A130392357C">Data1!$Z$1:$Z$10,Data1!$Z$12:$Z$32</definedName>
-    <definedName name="A130392357C_Data">Data1!$Z$12:$Z$32</definedName>
-    <definedName name="A130392357C_Latest">Data1!$Z$32</definedName>
-    <definedName name="A130393713F">Data1!$G$1:$G$10,Data1!$G$11:$G$32</definedName>
-    <definedName name="A130393713F_Data">Data1!$G$11:$G$32</definedName>
-    <definedName name="A130393713F_Latest">Data1!$G$32</definedName>
-    <definedName name="A130393714J">Data1!$P$1:$P$10,Data1!$P$23:$P$32</definedName>
-    <definedName name="A130393714J_Data">Data1!$P$23:$P$32</definedName>
-    <definedName name="A130393714J_Latest">Data1!$P$32</definedName>
-    <definedName name="A130393715K">Data1!$Y$1:$Y$10,Data1!$Y$12:$Y$32</definedName>
-    <definedName name="A130393715K_Data">Data1!$Y$12:$Y$32</definedName>
-    <definedName name="A130393715K_Latest">Data1!$Y$32</definedName>
-    <definedName name="A130393720C">Data1!$B$1:$B$10,Data1!$B$11:$B$32</definedName>
-    <definedName name="A130393720C_Data">Data1!$B$11:$B$32</definedName>
-    <definedName name="A130393720C_Latest">Data1!$B$32</definedName>
-    <definedName name="A130393721F">Data1!$K$1:$K$10,Data1!$K$23:$K$32</definedName>
-    <definedName name="A130393721F_Data">Data1!$K$23:$K$32</definedName>
-    <definedName name="A130393721F_Latest">Data1!$K$32</definedName>
-    <definedName name="A130393722J">Data1!$T$1:$T$10,Data1!$T$12:$T$32</definedName>
-    <definedName name="A130393722J_Data">Data1!$T$12:$T$32</definedName>
-    <definedName name="A130393722J_Latest">Data1!$T$32</definedName>
-    <definedName name="A130393727V">Data1!$J$1:$J$10,Data1!$J$11:$J$32</definedName>
-    <definedName name="A130393727V_Data">Data1!$J$11:$J$32</definedName>
-    <definedName name="A130393727V_Latest">Data1!$J$32</definedName>
-    <definedName name="A130393728W">Data1!$S$1:$S$10,Data1!$S$23:$S$32</definedName>
-    <definedName name="A130393728W_Data">Data1!$S$23:$S$32</definedName>
-    <definedName name="A130393728W_Latest">Data1!$S$32</definedName>
-    <definedName name="A130393729X">Data1!$AB$1:$AB$10,Data1!$AB$12:$AB$32</definedName>
-    <definedName name="A130393729X_Data">Data1!$AB$12:$AB$32</definedName>
-    <definedName name="A130393729X_Latest">Data1!$AB$32</definedName>
-    <definedName name="A130395001V">Data1!$F$1:$F$10,Data1!$F$11:$F$32</definedName>
-    <definedName name="A130395001V_Data">Data1!$F$11:$F$32</definedName>
-    <definedName name="A130395001V_Latest">Data1!$F$32</definedName>
-    <definedName name="A130395002W">Data1!$O$1:$O$10,Data1!$O$23:$O$32</definedName>
-    <definedName name="A130395002W_Data">Data1!$O$23:$O$32</definedName>
-    <definedName name="A130395002W_Latest">Data1!$O$32</definedName>
-    <definedName name="A130395003X">Data1!$X$1:$X$10,Data1!$X$12:$X$32</definedName>
-    <definedName name="A130395003X_Data">Data1!$X$12:$X$32</definedName>
-    <definedName name="A130395003X_Latest">Data1!$X$32</definedName>
-    <definedName name="A130395008K">Data1!$I$1:$I$10,Data1!$I$11:$I$32</definedName>
-    <definedName name="A130395008K_Data">Data1!$I$11:$I$32</definedName>
-    <definedName name="A130395008K_Latest">Data1!$I$32</definedName>
-    <definedName name="A130395009L">Data1!$R$1:$R$10,Data1!$R$23:$R$32</definedName>
-    <definedName name="A130395009L_Data">Data1!$R$23:$R$32</definedName>
-    <definedName name="A130395009L_Latest">Data1!$R$32</definedName>
-    <definedName name="A130395010W">Data1!$AA$1:$AA$10,Data1!$AA$12:$AA$32</definedName>
-    <definedName name="A130395010W_Data">Data1!$AA$12:$AA$32</definedName>
-    <definedName name="A130395010W_Latest">Data1!$AA$32</definedName>
-    <definedName name="A130396086K">Data1!$D$1:$D$10,Data1!$D$11:$D$32</definedName>
-    <definedName name="A130396086K_Data">Data1!$D$11:$D$32</definedName>
-    <definedName name="A130396086K_Latest">Data1!$D$32</definedName>
-    <definedName name="A130396087L">Data1!$M$1:$M$10,Data1!$M$23:$M$32</definedName>
-    <definedName name="A130396087L_Data">Data1!$M$23:$M$32</definedName>
-    <definedName name="A130396087L_Latest">Data1!$M$32</definedName>
-    <definedName name="A130396088R">Data1!$V$1:$V$10,Data1!$V$12:$V$32</definedName>
-    <definedName name="A130396088R_Data">Data1!$V$12:$V$32</definedName>
-    <definedName name="A130396088R_Latest">Data1!$V$32</definedName>
-    <definedName name="A130397375X">Data1!$C$1:$C$10,Data1!$C$11:$C$32</definedName>
-    <definedName name="A130397375X_Data">Data1!$C$11:$C$32</definedName>
-    <definedName name="A130397375X_Latest">Data1!$C$32</definedName>
-    <definedName name="A130397376A">Data1!$L$1:$L$10,Data1!$L$23:$L$32</definedName>
-    <definedName name="A130397376A_Data">Data1!$L$23:$L$32</definedName>
-    <definedName name="A130397376A_Latest">Data1!$L$32</definedName>
-    <definedName name="A130397377C">Data1!$U$1:$U$10,Data1!$U$12:$U$32</definedName>
-    <definedName name="A130397377C_Data">Data1!$U$12:$U$32</definedName>
-    <definedName name="A130397377C_Latest">Data1!$U$32</definedName>
-    <definedName name="A130397382W">Data1!$E$1:$E$10,Data1!$E$11:$E$32</definedName>
-    <definedName name="A130397382W_Data">Data1!$E$11:$E$32</definedName>
-    <definedName name="A130397382W_Latest">Data1!$E$32</definedName>
-    <definedName name="A130397383X">Data1!$N$1:$N$10,Data1!$N$23:$N$32</definedName>
-    <definedName name="A130397383X_Data">Data1!$N$23:$N$32</definedName>
-    <definedName name="A130397383X_Latest">Data1!$N$32</definedName>
-    <definedName name="A130397384A">Data1!$W$1:$W$10,Data1!$W$12:$W$32</definedName>
-    <definedName name="A130397384A_Data">Data1!$W$12:$W$32</definedName>
-    <definedName name="A130397384A_Latest">Data1!$W$32</definedName>
-    <definedName name="Date_Range">Data1!$A$2:$A$10,Data1!$A$11:$A$32</definedName>
-    <definedName name="Date_Range_Data">Data1!$A$11:$A$32</definedName>
+    <definedName name="A130392355X">Data1!$H$1:$H$10,Data1!$H$11:$H$33</definedName>
+    <definedName name="A130392355X_Data">Data1!$H$11:$H$33</definedName>
+    <definedName name="A130392355X_Latest">Data1!$H$33</definedName>
+    <definedName name="A130392356A">Data1!$Q$1:$Q$10,Data1!$Q$23:$Q$33</definedName>
+    <definedName name="A130392356A_Data">Data1!$Q$23:$Q$33</definedName>
+    <definedName name="A130392356A_Latest">Data1!$Q$33</definedName>
+    <definedName name="A130392357C">Data1!$Z$1:$Z$10,Data1!$Z$12:$Z$33</definedName>
+    <definedName name="A130392357C_Data">Data1!$Z$12:$Z$33</definedName>
+    <definedName name="A130392357C_Latest">Data1!$Z$33</definedName>
+    <definedName name="A130393713F">Data1!$G$1:$G$10,Data1!$G$11:$G$33</definedName>
+    <definedName name="A130393713F_Data">Data1!$G$11:$G$33</definedName>
+    <definedName name="A130393713F_Latest">Data1!$G$33</definedName>
+    <definedName name="A130393714J">Data1!$P$1:$P$10,Data1!$P$23:$P$33</definedName>
+    <definedName name="A130393714J_Data">Data1!$P$23:$P$33</definedName>
+    <definedName name="A130393714J_Latest">Data1!$P$33</definedName>
+    <definedName name="A130393715K">Data1!$Y$1:$Y$10,Data1!$Y$12:$Y$33</definedName>
+    <definedName name="A130393715K_Data">Data1!$Y$12:$Y$33</definedName>
+    <definedName name="A130393715K_Latest">Data1!$Y$33</definedName>
+    <definedName name="A130393720C">Data1!$B$1:$B$10,Data1!$B$11:$B$33</definedName>
+    <definedName name="A130393720C_Data">Data1!$B$11:$B$33</definedName>
+    <definedName name="A130393720C_Latest">Data1!$B$33</definedName>
+    <definedName name="A130393721F">Data1!$K$1:$K$10,Data1!$K$23:$K$33</definedName>
+    <definedName name="A130393721F_Data">Data1!$K$23:$K$33</definedName>
+    <definedName name="A130393721F_Latest">Data1!$K$33</definedName>
+    <definedName name="A130393722J">Data1!$T$1:$T$10,Data1!$T$12:$T$33</definedName>
+    <definedName name="A130393722J_Data">Data1!$T$12:$T$33</definedName>
+    <definedName name="A130393722J_Latest">Data1!$T$33</definedName>
+    <definedName name="A130393727V">Data1!$J$1:$J$10,Data1!$J$11:$J$33</definedName>
+    <definedName name="A130393727V_Data">Data1!$J$11:$J$33</definedName>
+    <definedName name="A130393727V_Latest">Data1!$J$33</definedName>
+    <definedName name="A130393728W">Data1!$S$1:$S$10,Data1!$S$23:$S$33</definedName>
+    <definedName name="A130393728W_Data">Data1!$S$23:$S$33</definedName>
+    <definedName name="A130393728W_Latest">Data1!$S$33</definedName>
+    <definedName name="A130393729X">Data1!$AB$1:$AB$10,Data1!$AB$12:$AB$33</definedName>
+    <definedName name="A130393729X_Data">Data1!$AB$12:$AB$33</definedName>
+    <definedName name="A130393729X_Latest">Data1!$AB$33</definedName>
+    <definedName name="A130395001V">Data1!$F$1:$F$10,Data1!$F$11:$F$33</definedName>
+    <definedName name="A130395001V_Data">Data1!$F$11:$F$33</definedName>
+    <definedName name="A130395001V_Latest">Data1!$F$33</definedName>
+    <definedName name="A130395002W">Data1!$O$1:$O$10,Data1!$O$23:$O$33</definedName>
+    <definedName name="A130395002W_Data">Data1!$O$23:$O$33</definedName>
+    <definedName name="A130395002W_Latest">Data1!$O$33</definedName>
+    <definedName name="A130395003X">Data1!$X$1:$X$10,Data1!$X$12:$X$33</definedName>
+    <definedName name="A130395003X_Data">Data1!$X$12:$X$33</definedName>
+    <definedName name="A130395003X_Latest">Data1!$X$33</definedName>
+    <definedName name="A130395008K">Data1!$I$1:$I$10,Data1!$I$11:$I$33</definedName>
+    <definedName name="A130395008K_Data">Data1!$I$11:$I$33</definedName>
+    <definedName name="A130395008K_Latest">Data1!$I$33</definedName>
+    <definedName name="A130395009L">Data1!$R$1:$R$10,Data1!$R$23:$R$33</definedName>
+    <definedName name="A130395009L_Data">Data1!$R$23:$R$33</definedName>
+    <definedName name="A130395009L_Latest">Data1!$R$33</definedName>
+    <definedName name="A130395010W">Data1!$AA$1:$AA$10,Data1!$AA$12:$AA$33</definedName>
+    <definedName name="A130395010W_Data">Data1!$AA$12:$AA$33</definedName>
+    <definedName name="A130395010W_Latest">Data1!$AA$33</definedName>
+    <definedName name="A130396086K">Data1!$D$1:$D$10,Data1!$D$11:$D$33</definedName>
+    <definedName name="A130396086K_Data">Data1!$D$11:$D$33</definedName>
+    <definedName name="A130396086K_Latest">Data1!$D$33</definedName>
+    <definedName name="A130396087L">Data1!$M$1:$M$10,Data1!$M$23:$M$33</definedName>
+    <definedName name="A130396087L_Data">Data1!$M$23:$M$33</definedName>
+    <definedName name="A130396087L_Latest">Data1!$M$33</definedName>
+    <definedName name="A130396088R">Data1!$V$1:$V$10,Data1!$V$12:$V$33</definedName>
+    <definedName name="A130396088R_Data">Data1!$V$12:$V$33</definedName>
+    <definedName name="A130396088R_Latest">Data1!$V$33</definedName>
+    <definedName name="A130397375X">Data1!$C$1:$C$10,Data1!$C$11:$C$33</definedName>
+    <definedName name="A130397375X_Data">Data1!$C$11:$C$33</definedName>
+    <definedName name="A130397375X_Latest">Data1!$C$33</definedName>
+    <definedName name="A130397376A">Data1!$L$1:$L$10,Data1!$L$23:$L$33</definedName>
+    <definedName name="A130397376A_Data">Data1!$L$23:$L$33</definedName>
+    <definedName name="A130397376A_Latest">Data1!$L$33</definedName>
+    <definedName name="A130397377C">Data1!$U$1:$U$10,Data1!$U$12:$U$33</definedName>
+    <definedName name="A130397377C_Data">Data1!$U$12:$U$33</definedName>
+    <definedName name="A130397377C_Latest">Data1!$U$33</definedName>
+    <definedName name="A130397382W">Data1!$E$1:$E$10,Data1!$E$11:$E$33</definedName>
+    <definedName name="A130397382W_Data">Data1!$E$11:$E$33</definedName>
+    <definedName name="A130397382W_Latest">Data1!$E$33</definedName>
+    <definedName name="A130397383X">Data1!$N$1:$N$10,Data1!$N$23:$N$33</definedName>
+    <definedName name="A130397383X_Data">Data1!$N$23:$N$33</definedName>
+    <definedName name="A130397383X_Latest">Data1!$N$33</definedName>
+    <definedName name="A130397384A">Data1!$W$1:$W$10,Data1!$W$12:$W$33</definedName>
+    <definedName name="A130397384A_Data">Data1!$W$12:$W$33</definedName>
+    <definedName name="A130397384A_Latest">Data1!$W$33</definedName>
+    <definedName name="Date_Range">Data1!$A$2:$A$10,Data1!$A$11:$A$33</definedName>
+    <definedName name="Date_Range_Data">Data1!$A$11:$A$33</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
@@ -1312,10 +1312,10 @@
         <v>45383</v>
       </c>
       <c r="G12" s="10">
-        <v>46023</v>
+        <v>46054</v>
       </c>
       <c r="H12" s="11">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I12" s="11" t="s">
         <v>36</v>
@@ -1344,10 +1344,10 @@
         <v>45383</v>
       </c>
       <c r="G13" s="10">
-        <v>46023</v>
+        <v>46054</v>
       </c>
       <c r="H13" s="11">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I13" s="11" t="s">
         <v>36</v>
@@ -1376,10 +1376,10 @@
         <v>45383</v>
       </c>
       <c r="G14" s="10">
-        <v>46023</v>
+        <v>46054</v>
       </c>
       <c r="H14" s="11">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I14" s="11" t="s">
         <v>36</v>
@@ -1408,10 +1408,10 @@
         <v>45383</v>
       </c>
       <c r="G15" s="10">
-        <v>46023</v>
+        <v>46054</v>
       </c>
       <c r="H15" s="11">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I15" s="11" t="s">
         <v>36</v>
@@ -1440,10 +1440,10 @@
         <v>45383</v>
       </c>
       <c r="G16" s="10">
-        <v>46023</v>
+        <v>46054</v>
       </c>
       <c r="H16" s="11">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I16" s="11" t="s">
         <v>36</v>
@@ -1472,10 +1472,10 @@
         <v>45383</v>
       </c>
       <c r="G17" s="10">
-        <v>46023</v>
+        <v>46054</v>
       </c>
       <c r="H17" s="11">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I17" s="11" t="s">
         <v>36</v>
@@ -1504,10 +1504,10 @@
         <v>45383</v>
       </c>
       <c r="G18" s="10">
-        <v>46023</v>
+        <v>46054</v>
       </c>
       <c r="H18" s="11">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I18" s="11" t="s">
         <v>36</v>
@@ -1536,10 +1536,10 @@
         <v>45383</v>
       </c>
       <c r="G19" s="10">
-        <v>46023</v>
+        <v>46054</v>
       </c>
       <c r="H19" s="11">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I19" s="11" t="s">
         <v>36</v>
@@ -1568,10 +1568,10 @@
         <v>45383</v>
       </c>
       <c r="G20" s="10">
-        <v>46023</v>
+        <v>46054</v>
       </c>
       <c r="H20" s="11">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I20" s="11" t="s">
         <v>36</v>
@@ -1600,10 +1600,10 @@
         <v>45748</v>
       </c>
       <c r="G21" s="10">
-        <v>46023</v>
+        <v>46054</v>
       </c>
       <c r="H21" s="11">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I21" s="11" t="s">
         <v>49</v>
@@ -1632,10 +1632,10 @@
         <v>45748</v>
       </c>
       <c r="G22" s="10">
-        <v>46023</v>
+        <v>46054</v>
       </c>
       <c r="H22" s="11">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I22" s="11" t="s">
         <v>49</v>
@@ -1664,10 +1664,10 @@
         <v>45748</v>
       </c>
       <c r="G23" s="10">
-        <v>46023</v>
+        <v>46054</v>
       </c>
       <c r="H23" s="11">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I23" s="11" t="s">
         <v>49</v>
@@ -1696,10 +1696,10 @@
         <v>45748</v>
       </c>
       <c r="G24" s="10">
-        <v>46023</v>
+        <v>46054</v>
       </c>
       <c r="H24" s="11">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I24" s="11" t="s">
         <v>49</v>
@@ -1728,10 +1728,10 @@
         <v>45748</v>
       </c>
       <c r="G25" s="10">
-        <v>46023</v>
+        <v>46054</v>
       </c>
       <c r="H25" s="11">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I25" s="11" t="s">
         <v>49</v>
@@ -1760,10 +1760,10 @@
         <v>45748</v>
       </c>
       <c r="G26" s="10">
-        <v>46023</v>
+        <v>46054</v>
       </c>
       <c r="H26" s="11">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I26" s="11" t="s">
         <v>49</v>
@@ -1792,10 +1792,10 @@
         <v>45748</v>
       </c>
       <c r="G27" s="10">
-        <v>46023</v>
+        <v>46054</v>
       </c>
       <c r="H27" s="11">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I27" s="11" t="s">
         <v>49</v>
@@ -1824,10 +1824,10 @@
         <v>45748</v>
       </c>
       <c r="G28" s="10">
-        <v>46023</v>
+        <v>46054</v>
       </c>
       <c r="H28" s="11">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I28" s="11" t="s">
         <v>49</v>
@@ -1856,10 +1856,10 @@
         <v>45748</v>
       </c>
       <c r="G29" s="10">
-        <v>46023</v>
+        <v>46054</v>
       </c>
       <c r="H29" s="11">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I29" s="11" t="s">
         <v>49</v>
@@ -1888,10 +1888,10 @@
         <v>45413</v>
       </c>
       <c r="G30" s="10">
-        <v>46023</v>
+        <v>46054</v>
       </c>
       <c r="H30" s="11">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I30" s="11" t="s">
         <v>49</v>
@@ -1920,10 +1920,10 @@
         <v>45413</v>
       </c>
       <c r="G31" s="10">
-        <v>46023</v>
+        <v>46054</v>
       </c>
       <c r="H31" s="11">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I31" s="11" t="s">
         <v>49</v>
@@ -1952,10 +1952,10 @@
         <v>45413</v>
       </c>
       <c r="G32" s="10">
-        <v>46023</v>
+        <v>46054</v>
       </c>
       <c r="H32" s="11">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I32" s="11" t="s">
         <v>49</v>
@@ -1984,10 +1984,10 @@
         <v>45413</v>
       </c>
       <c r="G33" s="10">
-        <v>46023</v>
+        <v>46054</v>
       </c>
       <c r="H33" s="11">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I33" s="11" t="s">
         <v>49</v>
@@ -2016,10 +2016,10 @@
         <v>45413</v>
       </c>
       <c r="G34" s="10">
-        <v>46023</v>
+        <v>46054</v>
       </c>
       <c r="H34" s="11">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I34" s="11" t="s">
         <v>49</v>
@@ -2048,10 +2048,10 @@
         <v>45413</v>
       </c>
       <c r="G35" s="10">
-        <v>46023</v>
+        <v>46054</v>
       </c>
       <c r="H35" s="11">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I35" s="11" t="s">
         <v>49</v>
@@ -2080,10 +2080,10 @@
         <v>45413</v>
       </c>
       <c r="G36" s="10">
-        <v>46023</v>
+        <v>46054</v>
       </c>
       <c r="H36" s="11">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I36" s="11" t="s">
         <v>49</v>
@@ -2112,10 +2112,10 @@
         <v>45413</v>
       </c>
       <c r="G37" s="10">
-        <v>46023</v>
+        <v>46054</v>
       </c>
       <c r="H37" s="11">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I37" s="11" t="s">
         <v>49</v>
@@ -2144,10 +2144,10 @@
         <v>45413</v>
       </c>
       <c r="G38" s="10">
-        <v>46023</v>
+        <v>46054</v>
       </c>
       <c r="H38" s="11">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I38" s="11" t="s">
         <v>49</v>
@@ -2209,7 +2209,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AB32"/>
+  <dimension ref="A1:AB33"/>
   <sheetFormatPr defaultColWidth="14.7109375" defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="16384" width="14.7109375" style="1"/>
@@ -2819,85 +2819,85 @@
         <v>33</v>
       </c>
       <c r="B8" s="6">
-        <v>46023</v>
+        <v>46054</v>
       </c>
       <c r="C8" s="6">
-        <v>46023</v>
+        <v>46054</v>
       </c>
       <c r="D8" s="6">
-        <v>46023</v>
+        <v>46054</v>
       </c>
       <c r="E8" s="6">
-        <v>46023</v>
+        <v>46054</v>
       </c>
       <c r="F8" s="6">
-        <v>46023</v>
+        <v>46054</v>
       </c>
       <c r="G8" s="6">
-        <v>46023</v>
+        <v>46054</v>
       </c>
       <c r="H8" s="6">
-        <v>46023</v>
+        <v>46054</v>
       </c>
       <c r="I8" s="6">
-        <v>46023</v>
+        <v>46054</v>
       </c>
       <c r="J8" s="6">
-        <v>46023</v>
+        <v>46054</v>
       </c>
       <c r="K8" s="6">
-        <v>46023</v>
+        <v>46054</v>
       </c>
       <c r="L8" s="6">
-        <v>46023</v>
+        <v>46054</v>
       </c>
       <c r="M8" s="6">
-        <v>46023</v>
+        <v>46054</v>
       </c>
       <c r="N8" s="6">
-        <v>46023</v>
+        <v>46054</v>
       </c>
       <c r="O8" s="6">
-        <v>46023</v>
+        <v>46054</v>
       </c>
       <c r="P8" s="6">
-        <v>46023</v>
+        <v>46054</v>
       </c>
       <c r="Q8" s="6">
-        <v>46023</v>
+        <v>46054</v>
       </c>
       <c r="R8" s="6">
-        <v>46023</v>
+        <v>46054</v>
       </c>
       <c r="S8" s="6">
-        <v>46023</v>
+        <v>46054</v>
       </c>
       <c r="T8" s="6">
-        <v>46023</v>
+        <v>46054</v>
       </c>
       <c r="U8" s="6">
-        <v>46023</v>
+        <v>46054</v>
       </c>
       <c r="V8" s="6">
-        <v>46023</v>
+        <v>46054</v>
       </c>
       <c r="W8" s="6">
-        <v>46023</v>
+        <v>46054</v>
       </c>
       <c r="X8" s="6">
-        <v>46023</v>
+        <v>46054</v>
       </c>
       <c r="Y8" s="6">
-        <v>46023</v>
+        <v>46054</v>
       </c>
       <c r="Z8" s="6">
-        <v>46023</v>
+        <v>46054</v>
       </c>
       <c r="AA8" s="6">
-        <v>46023</v>
+        <v>46054</v>
       </c>
       <c r="AB8" s="6">
-        <v>46023</v>
+        <v>46054</v>
       </c>
     </row>
     <row r="9" spans="1:28" x14ac:dyDescent="0.2">
@@ -2905,85 +2905,85 @@
         <v>34</v>
       </c>
       <c r="B9" s="1">
+        <v>23</v>
+      </c>
+      <c r="C9" s="1">
+        <v>23</v>
+      </c>
+      <c r="D9" s="1">
+        <v>23</v>
+      </c>
+      <c r="E9" s="1">
+        <v>23</v>
+      </c>
+      <c r="F9" s="1">
+        <v>23</v>
+      </c>
+      <c r="G9" s="1">
+        <v>23</v>
+      </c>
+      <c r="H9" s="1">
+        <v>23</v>
+      </c>
+      <c r="I9" s="1">
+        <v>23</v>
+      </c>
+      <c r="J9" s="1">
+        <v>23</v>
+      </c>
+      <c r="K9" s="1">
+        <v>11</v>
+      </c>
+      <c r="L9" s="1">
+        <v>11</v>
+      </c>
+      <c r="M9" s="1">
+        <v>11</v>
+      </c>
+      <c r="N9" s="1">
+        <v>11</v>
+      </c>
+      <c r="O9" s="1">
+        <v>11</v>
+      </c>
+      <c r="P9" s="1">
+        <v>11</v>
+      </c>
+      <c r="Q9" s="1">
+        <v>11</v>
+      </c>
+      <c r="R9" s="1">
+        <v>11</v>
+      </c>
+      <c r="S9" s="1">
+        <v>11</v>
+      </c>
+      <c r="T9" s="1">
         <v>22</v>
       </c>
-      <c r="C9" s="1">
+      <c r="U9" s="1">
         <v>22</v>
       </c>
-      <c r="D9" s="1">
+      <c r="V9" s="1">
         <v>22</v>
       </c>
-      <c r="E9" s="1">
+      <c r="W9" s="1">
         <v>22</v>
       </c>
-      <c r="F9" s="1">
+      <c r="X9" s="1">
         <v>22</v>
       </c>
-      <c r="G9" s="1">
+      <c r="Y9" s="1">
         <v>22</v>
       </c>
-      <c r="H9" s="1">
+      <c r="Z9" s="1">
         <v>22</v>
       </c>
-      <c r="I9" s="1">
+      <c r="AA9" s="1">
         <v>22</v>
       </c>
-      <c r="J9" s="1">
+      <c r="AB9" s="1">
         <v>22</v>
-      </c>
-      <c r="K9" s="1">
-        <v>10</v>
-      </c>
-      <c r="L9" s="1">
-        <v>10</v>
-      </c>
-      <c r="M9" s="1">
-        <v>10</v>
-      </c>
-      <c r="N9" s="1">
-        <v>10</v>
-      </c>
-      <c r="O9" s="1">
-        <v>10</v>
-      </c>
-      <c r="P9" s="1">
-        <v>10</v>
-      </c>
-      <c r="Q9" s="1">
-        <v>10</v>
-      </c>
-      <c r="R9" s="1">
-        <v>10</v>
-      </c>
-      <c r="S9" s="1">
-        <v>10</v>
-      </c>
-      <c r="T9" s="1">
-        <v>21</v>
-      </c>
-      <c r="U9" s="1">
-        <v>21</v>
-      </c>
-      <c r="V9" s="1">
-        <v>21</v>
-      </c>
-      <c r="W9" s="1">
-        <v>21</v>
-      </c>
-      <c r="X9" s="1">
-        <v>21</v>
-      </c>
-      <c r="Y9" s="1">
-        <v>21</v>
-      </c>
-      <c r="Z9" s="1">
-        <v>21</v>
-      </c>
-      <c r="AA9" s="1">
-        <v>21</v>
-      </c>
-      <c r="AB9" s="1">
-        <v>21</v>
       </c>
     </row>
     <row r="10" spans="1:28" x14ac:dyDescent="0.2">
@@ -4611,6 +4611,92 @@
       </c>
       <c r="AB32" s="9">
         <v>0.5</v>
+      </c>
+    </row>
+    <row r="33" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="A33" s="10">
+        <v>46054</v>
+      </c>
+      <c r="B33" s="8">
+        <v>101.31</v>
+      </c>
+      <c r="C33" s="8">
+        <v>101.4</v>
+      </c>
+      <c r="D33" s="8">
+        <v>101.36</v>
+      </c>
+      <c r="E33" s="8">
+        <v>101.05</v>
+      </c>
+      <c r="F33" s="8">
+        <v>101.41</v>
+      </c>
+      <c r="G33" s="8">
+        <v>101.21</v>
+      </c>
+      <c r="H33" s="8">
+        <v>101.46</v>
+      </c>
+      <c r="I33" s="8">
+        <v>100.91</v>
+      </c>
+      <c r="J33" s="8">
+        <v>101.42</v>
+      </c>
+      <c r="K33" s="9">
+        <v>3.7</v>
+      </c>
+      <c r="L33" s="9">
+        <v>3.8</v>
+      </c>
+      <c r="M33" s="9">
+        <v>3.3</v>
+      </c>
+      <c r="N33" s="9">
+        <v>3.7</v>
+      </c>
+      <c r="O33" s="9">
+        <v>3.4</v>
+      </c>
+      <c r="P33" s="9">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="Q33" s="9">
+        <v>4</v>
+      </c>
+      <c r="R33" s="9">
+        <v>3.2</v>
+      </c>
+      <c r="S33" s="9">
+        <v>3.5</v>
+      </c>
+      <c r="T33" s="9">
+        <v>0</v>
+      </c>
+      <c r="U33" s="9">
+        <v>-0.2</v>
+      </c>
+      <c r="V33" s="9">
+        <v>-0.1</v>
+      </c>
+      <c r="W33" s="9">
+        <v>0</v>
+      </c>
+      <c r="X33" s="9">
+        <v>0.1</v>
+      </c>
+      <c r="Y33" s="9">
+        <v>0.6</v>
+      </c>
+      <c r="Z33" s="9">
+        <v>0.2</v>
+      </c>
+      <c r="AA33" s="9">
+        <v>0.1</v>
+      </c>
+      <c r="AB33" s="9">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/data/raw/cpi.xlsx
+++ b/data/raw/cpi.xlsx
@@ -17,89 +17,89 @@
     <sheet name="Enquiries" sheetId="2" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="A130392355X">Data1!$H$1:$H$10,Data1!$H$11:$H$33</definedName>
-    <definedName name="A130392355X_Data">Data1!$H$11:$H$33</definedName>
-    <definedName name="A130392355X_Latest">Data1!$H$33</definedName>
-    <definedName name="A130392356A">Data1!$Q$1:$Q$10,Data1!$Q$23:$Q$33</definedName>
-    <definedName name="A130392356A_Data">Data1!$Q$23:$Q$33</definedName>
-    <definedName name="A130392356A_Latest">Data1!$Q$33</definedName>
-    <definedName name="A130392357C">Data1!$Z$1:$Z$10,Data1!$Z$12:$Z$33</definedName>
-    <definedName name="A130392357C_Data">Data1!$Z$12:$Z$33</definedName>
-    <definedName name="A130392357C_Latest">Data1!$Z$33</definedName>
-    <definedName name="A130393713F">Data1!$G$1:$G$10,Data1!$G$11:$G$33</definedName>
-    <definedName name="A130393713F_Data">Data1!$G$11:$G$33</definedName>
-    <definedName name="A130393713F_Latest">Data1!$G$33</definedName>
-    <definedName name="A130393714J">Data1!$P$1:$P$10,Data1!$P$23:$P$33</definedName>
-    <definedName name="A130393714J_Data">Data1!$P$23:$P$33</definedName>
-    <definedName name="A130393714J_Latest">Data1!$P$33</definedName>
-    <definedName name="A130393715K">Data1!$Y$1:$Y$10,Data1!$Y$12:$Y$33</definedName>
-    <definedName name="A130393715K_Data">Data1!$Y$12:$Y$33</definedName>
-    <definedName name="A130393715K_Latest">Data1!$Y$33</definedName>
-    <definedName name="A130393720C">Data1!$B$1:$B$10,Data1!$B$11:$B$33</definedName>
-    <definedName name="A130393720C_Data">Data1!$B$11:$B$33</definedName>
-    <definedName name="A130393720C_Latest">Data1!$B$33</definedName>
-    <definedName name="A130393721F">Data1!$K$1:$K$10,Data1!$K$23:$K$33</definedName>
-    <definedName name="A130393721F_Data">Data1!$K$23:$K$33</definedName>
-    <definedName name="A130393721F_Latest">Data1!$K$33</definedName>
-    <definedName name="A130393722J">Data1!$T$1:$T$10,Data1!$T$12:$T$33</definedName>
-    <definedName name="A130393722J_Data">Data1!$T$12:$T$33</definedName>
-    <definedName name="A130393722J_Latest">Data1!$T$33</definedName>
-    <definedName name="A130393727V">Data1!$J$1:$J$10,Data1!$J$11:$J$33</definedName>
-    <definedName name="A130393727V_Data">Data1!$J$11:$J$33</definedName>
-    <definedName name="A130393727V_Latest">Data1!$J$33</definedName>
-    <definedName name="A130393728W">Data1!$S$1:$S$10,Data1!$S$23:$S$33</definedName>
-    <definedName name="A130393728W_Data">Data1!$S$23:$S$33</definedName>
-    <definedName name="A130393728W_Latest">Data1!$S$33</definedName>
-    <definedName name="A130393729X">Data1!$AB$1:$AB$10,Data1!$AB$12:$AB$33</definedName>
-    <definedName name="A130393729X_Data">Data1!$AB$12:$AB$33</definedName>
-    <definedName name="A130393729X_Latest">Data1!$AB$33</definedName>
-    <definedName name="A130395001V">Data1!$F$1:$F$10,Data1!$F$11:$F$33</definedName>
-    <definedName name="A130395001V_Data">Data1!$F$11:$F$33</definedName>
-    <definedName name="A130395001V_Latest">Data1!$F$33</definedName>
-    <definedName name="A130395002W">Data1!$O$1:$O$10,Data1!$O$23:$O$33</definedName>
-    <definedName name="A130395002W_Data">Data1!$O$23:$O$33</definedName>
-    <definedName name="A130395002W_Latest">Data1!$O$33</definedName>
-    <definedName name="A130395003X">Data1!$X$1:$X$10,Data1!$X$12:$X$33</definedName>
-    <definedName name="A130395003X_Data">Data1!$X$12:$X$33</definedName>
-    <definedName name="A130395003X_Latest">Data1!$X$33</definedName>
-    <definedName name="A130395008K">Data1!$I$1:$I$10,Data1!$I$11:$I$33</definedName>
-    <definedName name="A130395008K_Data">Data1!$I$11:$I$33</definedName>
-    <definedName name="A130395008K_Latest">Data1!$I$33</definedName>
-    <definedName name="A130395009L">Data1!$R$1:$R$10,Data1!$R$23:$R$33</definedName>
-    <definedName name="A130395009L_Data">Data1!$R$23:$R$33</definedName>
-    <definedName name="A130395009L_Latest">Data1!$R$33</definedName>
-    <definedName name="A130395010W">Data1!$AA$1:$AA$10,Data1!$AA$12:$AA$33</definedName>
-    <definedName name="A130395010W_Data">Data1!$AA$12:$AA$33</definedName>
-    <definedName name="A130395010W_Latest">Data1!$AA$33</definedName>
-    <definedName name="A130396086K">Data1!$D$1:$D$10,Data1!$D$11:$D$33</definedName>
-    <definedName name="A130396086K_Data">Data1!$D$11:$D$33</definedName>
-    <definedName name="A130396086K_Latest">Data1!$D$33</definedName>
-    <definedName name="A130396087L">Data1!$M$1:$M$10,Data1!$M$23:$M$33</definedName>
-    <definedName name="A130396087L_Data">Data1!$M$23:$M$33</definedName>
-    <definedName name="A130396087L_Latest">Data1!$M$33</definedName>
-    <definedName name="A130396088R">Data1!$V$1:$V$10,Data1!$V$12:$V$33</definedName>
-    <definedName name="A130396088R_Data">Data1!$V$12:$V$33</definedName>
-    <definedName name="A130396088R_Latest">Data1!$V$33</definedName>
-    <definedName name="A130397375X">Data1!$C$1:$C$10,Data1!$C$11:$C$33</definedName>
-    <definedName name="A130397375X_Data">Data1!$C$11:$C$33</definedName>
-    <definedName name="A130397375X_Latest">Data1!$C$33</definedName>
-    <definedName name="A130397376A">Data1!$L$1:$L$10,Data1!$L$23:$L$33</definedName>
-    <definedName name="A130397376A_Data">Data1!$L$23:$L$33</definedName>
-    <definedName name="A130397376A_Latest">Data1!$L$33</definedName>
-    <definedName name="A130397377C">Data1!$U$1:$U$10,Data1!$U$12:$U$33</definedName>
-    <definedName name="A130397377C_Data">Data1!$U$12:$U$33</definedName>
-    <definedName name="A130397377C_Latest">Data1!$U$33</definedName>
-    <definedName name="A130397382W">Data1!$E$1:$E$10,Data1!$E$11:$E$33</definedName>
-    <definedName name="A130397382W_Data">Data1!$E$11:$E$33</definedName>
-    <definedName name="A130397382W_Latest">Data1!$E$33</definedName>
-    <definedName name="A130397383X">Data1!$N$1:$N$10,Data1!$N$23:$N$33</definedName>
-    <definedName name="A130397383X_Data">Data1!$N$23:$N$33</definedName>
-    <definedName name="A130397383X_Latest">Data1!$N$33</definedName>
-    <definedName name="A130397384A">Data1!$W$1:$W$10,Data1!$W$12:$W$33</definedName>
-    <definedName name="A130397384A_Data">Data1!$W$12:$W$33</definedName>
-    <definedName name="A130397384A_Latest">Data1!$W$33</definedName>
-    <definedName name="Date_Range">Data1!$A$2:$A$10,Data1!$A$11:$A$33</definedName>
-    <definedName name="Date_Range_Data">Data1!$A$11:$A$33</definedName>
+    <definedName name="A130392355X">Data1!$H$1:$H$10,Data1!$H$11:$H$34</definedName>
+    <definedName name="A130392355X_Data">Data1!$H$11:$H$34</definedName>
+    <definedName name="A130392355X_Latest">Data1!$H$34</definedName>
+    <definedName name="A130392356A">Data1!$Q$1:$Q$10,Data1!$Q$23:$Q$34</definedName>
+    <definedName name="A130392356A_Data">Data1!$Q$23:$Q$34</definedName>
+    <definedName name="A130392356A_Latest">Data1!$Q$34</definedName>
+    <definedName name="A130392357C">Data1!$Z$1:$Z$10,Data1!$Z$12:$Z$34</definedName>
+    <definedName name="A130392357C_Data">Data1!$Z$12:$Z$34</definedName>
+    <definedName name="A130392357C_Latest">Data1!$Z$34</definedName>
+    <definedName name="A130393713F">Data1!$G$1:$G$10,Data1!$G$11:$G$34</definedName>
+    <definedName name="A130393713F_Data">Data1!$G$11:$G$34</definedName>
+    <definedName name="A130393713F_Latest">Data1!$G$34</definedName>
+    <definedName name="A130393714J">Data1!$P$1:$P$10,Data1!$P$23:$P$34</definedName>
+    <definedName name="A130393714J_Data">Data1!$P$23:$P$34</definedName>
+    <definedName name="A130393714J_Latest">Data1!$P$34</definedName>
+    <definedName name="A130393715K">Data1!$Y$1:$Y$10,Data1!$Y$12:$Y$34</definedName>
+    <definedName name="A130393715K_Data">Data1!$Y$12:$Y$34</definedName>
+    <definedName name="A130393715K_Latest">Data1!$Y$34</definedName>
+    <definedName name="A130393720C">Data1!$B$1:$B$10,Data1!$B$11:$B$34</definedName>
+    <definedName name="A130393720C_Data">Data1!$B$11:$B$34</definedName>
+    <definedName name="A130393720C_Latest">Data1!$B$34</definedName>
+    <definedName name="A130393721F">Data1!$K$1:$K$10,Data1!$K$23:$K$34</definedName>
+    <definedName name="A130393721F_Data">Data1!$K$23:$K$34</definedName>
+    <definedName name="A130393721F_Latest">Data1!$K$34</definedName>
+    <definedName name="A130393722J">Data1!$T$1:$T$10,Data1!$T$12:$T$34</definedName>
+    <definedName name="A130393722J_Data">Data1!$T$12:$T$34</definedName>
+    <definedName name="A130393722J_Latest">Data1!$T$34</definedName>
+    <definedName name="A130393727V">Data1!$J$1:$J$10,Data1!$J$11:$J$34</definedName>
+    <definedName name="A130393727V_Data">Data1!$J$11:$J$34</definedName>
+    <definedName name="A130393727V_Latest">Data1!$J$34</definedName>
+    <definedName name="A130393728W">Data1!$S$1:$S$10,Data1!$S$23:$S$34</definedName>
+    <definedName name="A130393728W_Data">Data1!$S$23:$S$34</definedName>
+    <definedName name="A130393728W_Latest">Data1!$S$34</definedName>
+    <definedName name="A130393729X">Data1!$AB$1:$AB$10,Data1!$AB$12:$AB$34</definedName>
+    <definedName name="A130393729X_Data">Data1!$AB$12:$AB$34</definedName>
+    <definedName name="A130393729X_Latest">Data1!$AB$34</definedName>
+    <definedName name="A130395001V">Data1!$F$1:$F$10,Data1!$F$11:$F$34</definedName>
+    <definedName name="A130395001V_Data">Data1!$F$11:$F$34</definedName>
+    <definedName name="A130395001V_Latest">Data1!$F$34</definedName>
+    <definedName name="A130395002W">Data1!$O$1:$O$10,Data1!$O$23:$O$34</definedName>
+    <definedName name="A130395002W_Data">Data1!$O$23:$O$34</definedName>
+    <definedName name="A130395002W_Latest">Data1!$O$34</definedName>
+    <definedName name="A130395003X">Data1!$X$1:$X$10,Data1!$X$12:$X$34</definedName>
+    <definedName name="A130395003X_Data">Data1!$X$12:$X$34</definedName>
+    <definedName name="A130395003X_Latest">Data1!$X$34</definedName>
+    <definedName name="A130395008K">Data1!$I$1:$I$10,Data1!$I$11:$I$34</definedName>
+    <definedName name="A130395008K_Data">Data1!$I$11:$I$34</definedName>
+    <definedName name="A130395008K_Latest">Data1!$I$34</definedName>
+    <definedName name="A130395009L">Data1!$R$1:$R$10,Data1!$R$23:$R$34</definedName>
+    <definedName name="A130395009L_Data">Data1!$R$23:$R$34</definedName>
+    <definedName name="A130395009L_Latest">Data1!$R$34</definedName>
+    <definedName name="A130395010W">Data1!$AA$1:$AA$10,Data1!$AA$12:$AA$34</definedName>
+    <definedName name="A130395010W_Data">Data1!$AA$12:$AA$34</definedName>
+    <definedName name="A130395010W_Latest">Data1!$AA$34</definedName>
+    <definedName name="A130396086K">Data1!$D$1:$D$10,Data1!$D$11:$D$34</definedName>
+    <definedName name="A130396086K_Data">Data1!$D$11:$D$34</definedName>
+    <definedName name="A130396086K_Latest">Data1!$D$34</definedName>
+    <definedName name="A130396087L">Data1!$M$1:$M$10,Data1!$M$23:$M$34</definedName>
+    <definedName name="A130396087L_Data">Data1!$M$23:$M$34</definedName>
+    <definedName name="A130396087L_Latest">Data1!$M$34</definedName>
+    <definedName name="A130396088R">Data1!$V$1:$V$10,Data1!$V$12:$V$34</definedName>
+    <definedName name="A130396088R_Data">Data1!$V$12:$V$34</definedName>
+    <definedName name="A130396088R_Latest">Data1!$V$34</definedName>
+    <definedName name="A130397375X">Data1!$C$1:$C$10,Data1!$C$11:$C$34</definedName>
+    <definedName name="A130397375X_Data">Data1!$C$11:$C$34</definedName>
+    <definedName name="A130397375X_Latest">Data1!$C$34</definedName>
+    <definedName name="A130397376A">Data1!$L$1:$L$10,Data1!$L$23:$L$34</definedName>
+    <definedName name="A130397376A_Data">Data1!$L$23:$L$34</definedName>
+    <definedName name="A130397376A_Latest">Data1!$L$34</definedName>
+    <definedName name="A130397377C">Data1!$U$1:$U$10,Data1!$U$12:$U$34</definedName>
+    <definedName name="A130397377C_Data">Data1!$U$12:$U$34</definedName>
+    <definedName name="A130397377C_Latest">Data1!$U$34</definedName>
+    <definedName name="A130397382W">Data1!$E$1:$E$10,Data1!$E$11:$E$34</definedName>
+    <definedName name="A130397382W_Data">Data1!$E$11:$E$34</definedName>
+    <definedName name="A130397382W_Latest">Data1!$E$34</definedName>
+    <definedName name="A130397383X">Data1!$N$1:$N$10,Data1!$N$23:$N$34</definedName>
+    <definedName name="A130397383X_Data">Data1!$N$23:$N$34</definedName>
+    <definedName name="A130397383X_Latest">Data1!$N$34</definedName>
+    <definedName name="A130397384A">Data1!$W$1:$W$10,Data1!$W$12:$W$34</definedName>
+    <definedName name="A130397384A_Data">Data1!$W$12:$W$34</definedName>
+    <definedName name="A130397384A_Latest">Data1!$W$34</definedName>
+    <definedName name="Date_Range">Data1!$A$2:$A$10,Data1!$A$11:$A$34</definedName>
+    <definedName name="Date_Range_Data">Data1!$A$11:$A$34</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
@@ -1312,10 +1312,10 @@
         <v>45383</v>
       </c>
       <c r="G12" s="10">
-        <v>46054</v>
+        <v>46082</v>
       </c>
       <c r="H12" s="11">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I12" s="11" t="s">
         <v>36</v>
@@ -1344,10 +1344,10 @@
         <v>45383</v>
       </c>
       <c r="G13" s="10">
-        <v>46054</v>
+        <v>46082</v>
       </c>
       <c r="H13" s="11">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I13" s="11" t="s">
         <v>36</v>
@@ -1376,10 +1376,10 @@
         <v>45383</v>
       </c>
       <c r="G14" s="10">
-        <v>46054</v>
+        <v>46082</v>
       </c>
       <c r="H14" s="11">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I14" s="11" t="s">
         <v>36</v>
@@ -1408,10 +1408,10 @@
         <v>45383</v>
       </c>
       <c r="G15" s="10">
-        <v>46054</v>
+        <v>46082</v>
       </c>
       <c r="H15" s="11">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I15" s="11" t="s">
         <v>36</v>
@@ -1440,10 +1440,10 @@
         <v>45383</v>
       </c>
       <c r="G16" s="10">
-        <v>46054</v>
+        <v>46082</v>
       </c>
       <c r="H16" s="11">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I16" s="11" t="s">
         <v>36</v>
@@ -1472,10 +1472,10 @@
         <v>45383</v>
       </c>
       <c r="G17" s="10">
-        <v>46054</v>
+        <v>46082</v>
       </c>
       <c r="H17" s="11">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I17" s="11" t="s">
         <v>36</v>
@@ -1504,10 +1504,10 @@
         <v>45383</v>
       </c>
       <c r="G18" s="10">
-        <v>46054</v>
+        <v>46082</v>
       </c>
       <c r="H18" s="11">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I18" s="11" t="s">
         <v>36</v>
@@ -1536,10 +1536,10 @@
         <v>45383</v>
       </c>
       <c r="G19" s="10">
-        <v>46054</v>
+        <v>46082</v>
       </c>
       <c r="H19" s="11">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I19" s="11" t="s">
         <v>36</v>
@@ -1568,10 +1568,10 @@
         <v>45383</v>
       </c>
       <c r="G20" s="10">
-        <v>46054</v>
+        <v>46082</v>
       </c>
       <c r="H20" s="11">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I20" s="11" t="s">
         <v>36</v>
@@ -1600,10 +1600,10 @@
         <v>45748</v>
       </c>
       <c r="G21" s="10">
-        <v>46054</v>
+        <v>46082</v>
       </c>
       <c r="H21" s="11">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I21" s="11" t="s">
         <v>49</v>
@@ -1632,10 +1632,10 @@
         <v>45748</v>
       </c>
       <c r="G22" s="10">
-        <v>46054</v>
+        <v>46082</v>
       </c>
       <c r="H22" s="11">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I22" s="11" t="s">
         <v>49</v>
@@ -1664,10 +1664,10 @@
         <v>45748</v>
       </c>
       <c r="G23" s="10">
-        <v>46054</v>
+        <v>46082</v>
       </c>
       <c r="H23" s="11">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I23" s="11" t="s">
         <v>49</v>
@@ -1696,10 +1696,10 @@
         <v>45748</v>
       </c>
       <c r="G24" s="10">
-        <v>46054</v>
+        <v>46082</v>
       </c>
       <c r="H24" s="11">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I24" s="11" t="s">
         <v>49</v>
@@ -1728,10 +1728,10 @@
         <v>45748</v>
       </c>
       <c r="G25" s="10">
-        <v>46054</v>
+        <v>46082</v>
       </c>
       <c r="H25" s="11">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I25" s="11" t="s">
         <v>49</v>
@@ -1760,10 +1760,10 @@
         <v>45748</v>
       </c>
       <c r="G26" s="10">
-        <v>46054</v>
+        <v>46082</v>
       </c>
       <c r="H26" s="11">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I26" s="11" t="s">
         <v>49</v>
@@ -1792,10 +1792,10 @@
         <v>45748</v>
       </c>
       <c r="G27" s="10">
-        <v>46054</v>
+        <v>46082</v>
       </c>
       <c r="H27" s="11">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I27" s="11" t="s">
         <v>49</v>
@@ -1824,10 +1824,10 @@
         <v>45748</v>
       </c>
       <c r="G28" s="10">
-        <v>46054</v>
+        <v>46082</v>
       </c>
       <c r="H28" s="11">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I28" s="11" t="s">
         <v>49</v>
@@ -1856,10 +1856,10 @@
         <v>45748</v>
       </c>
       <c r="G29" s="10">
-        <v>46054</v>
+        <v>46082</v>
       </c>
       <c r="H29" s="11">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I29" s="11" t="s">
         <v>49</v>
@@ -1888,10 +1888,10 @@
         <v>45413</v>
       </c>
       <c r="G30" s="10">
-        <v>46054</v>
+        <v>46082</v>
       </c>
       <c r="H30" s="11">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I30" s="11" t="s">
         <v>49</v>
@@ -1920,10 +1920,10 @@
         <v>45413</v>
       </c>
       <c r="G31" s="10">
-        <v>46054</v>
+        <v>46082</v>
       </c>
       <c r="H31" s="11">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I31" s="11" t="s">
         <v>49</v>
@@ -1952,10 +1952,10 @@
         <v>45413</v>
       </c>
       <c r="G32" s="10">
-        <v>46054</v>
+        <v>46082</v>
       </c>
       <c r="H32" s="11">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I32" s="11" t="s">
         <v>49</v>
@@ -1984,10 +1984,10 @@
         <v>45413</v>
       </c>
       <c r="G33" s="10">
-        <v>46054</v>
+        <v>46082</v>
       </c>
       <c r="H33" s="11">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I33" s="11" t="s">
         <v>49</v>
@@ -2016,10 +2016,10 @@
         <v>45413</v>
       </c>
       <c r="G34" s="10">
-        <v>46054</v>
+        <v>46082</v>
       </c>
       <c r="H34" s="11">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I34" s="11" t="s">
         <v>49</v>
@@ -2048,10 +2048,10 @@
         <v>45413</v>
       </c>
       <c r="G35" s="10">
-        <v>46054</v>
+        <v>46082</v>
       </c>
       <c r="H35" s="11">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I35" s="11" t="s">
         <v>49</v>
@@ -2080,10 +2080,10 @@
         <v>45413</v>
       </c>
       <c r="G36" s="10">
-        <v>46054</v>
+        <v>46082</v>
       </c>
       <c r="H36" s="11">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I36" s="11" t="s">
         <v>49</v>
@@ -2112,10 +2112,10 @@
         <v>45413</v>
       </c>
       <c r="G37" s="10">
-        <v>46054</v>
+        <v>46082</v>
       </c>
       <c r="H37" s="11">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I37" s="11" t="s">
         <v>49</v>
@@ -2144,10 +2144,10 @@
         <v>45413</v>
       </c>
       <c r="G38" s="10">
-        <v>46054</v>
+        <v>46082</v>
       </c>
       <c r="H38" s="11">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I38" s="11" t="s">
         <v>49</v>
@@ -2209,7 +2209,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AB33"/>
+  <dimension ref="A1:AB34"/>
   <sheetFormatPr defaultColWidth="14.7109375" defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="16384" width="14.7109375" style="1"/>
@@ -2819,85 +2819,85 @@
         <v>33</v>
       </c>
       <c r="B8" s="6">
-        <v>46054</v>
+        <v>46082</v>
       </c>
       <c r="C8" s="6">
-        <v>46054</v>
+        <v>46082</v>
       </c>
       <c r="D8" s="6">
-        <v>46054</v>
+        <v>46082</v>
       </c>
       <c r="E8" s="6">
-        <v>46054</v>
+        <v>46082</v>
       </c>
       <c r="F8" s="6">
-        <v>46054</v>
+        <v>46082</v>
       </c>
       <c r="G8" s="6">
-        <v>46054</v>
+        <v>46082</v>
       </c>
       <c r="H8" s="6">
-        <v>46054</v>
+        <v>46082</v>
       </c>
       <c r="I8" s="6">
-        <v>46054</v>
+        <v>46082</v>
       </c>
       <c r="J8" s="6">
-        <v>46054</v>
+        <v>46082</v>
       </c>
       <c r="K8" s="6">
-        <v>46054</v>
+        <v>46082</v>
       </c>
       <c r="L8" s="6">
-        <v>46054</v>
+        <v>46082</v>
       </c>
       <c r="M8" s="6">
-        <v>46054</v>
+        <v>46082</v>
       </c>
       <c r="N8" s="6">
-        <v>46054</v>
+        <v>46082</v>
       </c>
       <c r="O8" s="6">
-        <v>46054</v>
+        <v>46082</v>
       </c>
       <c r="P8" s="6">
-        <v>46054</v>
+        <v>46082</v>
       </c>
       <c r="Q8" s="6">
-        <v>46054</v>
+        <v>46082</v>
       </c>
       <c r="R8" s="6">
-        <v>46054</v>
+        <v>46082</v>
       </c>
       <c r="S8" s="6">
-        <v>46054</v>
+        <v>46082</v>
       </c>
       <c r="T8" s="6">
-        <v>46054</v>
+        <v>46082</v>
       </c>
       <c r="U8" s="6">
-        <v>46054</v>
+        <v>46082</v>
       </c>
       <c r="V8" s="6">
-        <v>46054</v>
+        <v>46082</v>
       </c>
       <c r="W8" s="6">
-        <v>46054</v>
+        <v>46082</v>
       </c>
       <c r="X8" s="6">
-        <v>46054</v>
+        <v>46082</v>
       </c>
       <c r="Y8" s="6">
-        <v>46054</v>
+        <v>46082</v>
       </c>
       <c r="Z8" s="6">
-        <v>46054</v>
+        <v>46082</v>
       </c>
       <c r="AA8" s="6">
-        <v>46054</v>
+        <v>46082</v>
       </c>
       <c r="AB8" s="6">
-        <v>46054</v>
+        <v>46082</v>
       </c>
     </row>
     <row r="9" spans="1:28" x14ac:dyDescent="0.2">
@@ -2905,85 +2905,85 @@
         <v>34</v>
       </c>
       <c r="B9" s="1">
+        <v>24</v>
+      </c>
+      <c r="C9" s="1">
+        <v>24</v>
+      </c>
+      <c r="D9" s="1">
+        <v>24</v>
+      </c>
+      <c r="E9" s="1">
+        <v>24</v>
+      </c>
+      <c r="F9" s="1">
+        <v>24</v>
+      </c>
+      <c r="G9" s="1">
+        <v>24</v>
+      </c>
+      <c r="H9" s="1">
+        <v>24</v>
+      </c>
+      <c r="I9" s="1">
+        <v>24</v>
+      </c>
+      <c r="J9" s="1">
+        <v>24</v>
+      </c>
+      <c r="K9" s="1">
+        <v>12</v>
+      </c>
+      <c r="L9" s="1">
+        <v>12</v>
+      </c>
+      <c r="M9" s="1">
+        <v>12</v>
+      </c>
+      <c r="N9" s="1">
+        <v>12</v>
+      </c>
+      <c r="O9" s="1">
+        <v>12</v>
+      </c>
+      <c r="P9" s="1">
+        <v>12</v>
+      </c>
+      <c r="Q9" s="1">
+        <v>12</v>
+      </c>
+      <c r="R9" s="1">
+        <v>12</v>
+      </c>
+      <c r="S9" s="1">
+        <v>12</v>
+      </c>
+      <c r="T9" s="1">
         <v>23</v>
       </c>
-      <c r="C9" s="1">
+      <c r="U9" s="1">
         <v>23</v>
       </c>
-      <c r="D9" s="1">
+      <c r="V9" s="1">
         <v>23</v>
       </c>
-      <c r="E9" s="1">
+      <c r="W9" s="1">
         <v>23</v>
       </c>
-      <c r="F9" s="1">
+      <c r="X9" s="1">
         <v>23</v>
       </c>
-      <c r="G9" s="1">
+      <c r="Y9" s="1">
         <v>23</v>
       </c>
-      <c r="H9" s="1">
+      <c r="Z9" s="1">
         <v>23</v>
       </c>
-      <c r="I9" s="1">
+      <c r="AA9" s="1">
         <v>23</v>
       </c>
-      <c r="J9" s="1">
+      <c r="AB9" s="1">
         <v>23</v>
-      </c>
-      <c r="K9" s="1">
-        <v>11</v>
-      </c>
-      <c r="L9" s="1">
-        <v>11</v>
-      </c>
-      <c r="M9" s="1">
-        <v>11</v>
-      </c>
-      <c r="N9" s="1">
-        <v>11</v>
-      </c>
-      <c r="O9" s="1">
-        <v>11</v>
-      </c>
-      <c r="P9" s="1">
-        <v>11</v>
-      </c>
-      <c r="Q9" s="1">
-        <v>11</v>
-      </c>
-      <c r="R9" s="1">
-        <v>11</v>
-      </c>
-      <c r="S9" s="1">
-        <v>11</v>
-      </c>
-      <c r="T9" s="1">
-        <v>22</v>
-      </c>
-      <c r="U9" s="1">
-        <v>22</v>
-      </c>
-      <c r="V9" s="1">
-        <v>22</v>
-      </c>
-      <c r="W9" s="1">
-        <v>22</v>
-      </c>
-      <c r="X9" s="1">
-        <v>22</v>
-      </c>
-      <c r="Y9" s="1">
-        <v>22</v>
-      </c>
-      <c r="Z9" s="1">
-        <v>22</v>
-      </c>
-      <c r="AA9" s="1">
-        <v>22</v>
-      </c>
-      <c r="AB9" s="1">
-        <v>22</v>
       </c>
     </row>
     <row r="10" spans="1:28" x14ac:dyDescent="0.2">
@@ -4697,6 +4697,92 @@
       </c>
       <c r="AB33" s="9">
         <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="A34" s="10">
+        <v>46082</v>
+      </c>
+      <c r="B34" s="8">
+        <v>102.44</v>
+      </c>
+      <c r="C34" s="8">
+        <v>102.41</v>
+      </c>
+      <c r="D34" s="8">
+        <v>102.57</v>
+      </c>
+      <c r="E34" s="8">
+        <v>102.14</v>
+      </c>
+      <c r="F34" s="8">
+        <v>102.7</v>
+      </c>
+      <c r="G34" s="8">
+        <v>102.45</v>
+      </c>
+      <c r="H34" s="8">
+        <v>102.82</v>
+      </c>
+      <c r="I34" s="8">
+        <v>102.08</v>
+      </c>
+      <c r="J34" s="8">
+        <v>102.25</v>
+      </c>
+      <c r="K34" s="9">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="L34" s="9">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="M34" s="9">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="N34" s="9">
+        <v>4.7</v>
+      </c>
+      <c r="O34" s="9">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="P34" s="9">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="Q34" s="9">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="R34" s="9">
+        <v>4.2</v>
+      </c>
+      <c r="S34" s="9">
+        <v>4.2</v>
+      </c>
+      <c r="T34" s="9">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="U34" s="9">
+        <v>1</v>
+      </c>
+      <c r="V34" s="9">
+        <v>1.2</v>
+      </c>
+      <c r="W34" s="9">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="X34" s="9">
+        <v>1.3</v>
+      </c>
+      <c r="Y34" s="9">
+        <v>1.2</v>
+      </c>
+      <c r="Z34" s="9">
+        <v>1.3</v>
+      </c>
+      <c r="AA34" s="9">
+        <v>1.2</v>
+      </c>
+      <c r="AB34" s="9">
+        <v>0.8</v>
       </c>
     </row>
   </sheetData>
